--- a/StructureDefinition-cover-test.xlsx
+++ b/StructureDefinition-cover-test.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-cover-test.xlsx
+++ b/StructureDefinition-cover-test.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1976,17 +1976,17 @@
   <dimension ref="A1:AP78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.86328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.8125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1995,28 +1995,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.55078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-cover-test.xlsx
+++ b/StructureDefinition-cover-test.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3073" uniqueCount="527">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:17:00-03:00</t>
+    <t>2026-10-20T20:13:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Represents a cover test result, performed with or without correction, at
-near or far distance. Findings are recorded as open text/coded values for now (PC:
-orthophoria, PL: various movement patterns), since no confirmed SNOMED/LOINC binding has
+    <t>Represents a cover test result, performed with or without correction, at
+near or far distance. Findings are recorded as open text/coded values for now (PC:
+orthophoria, PL: various movement patterns), since no confirmed SNOMED/LOINC binding has
 been verified for these specific findings yet.</t>
   </si>
   <si>
@@ -632,6 +632,31 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:exam</t>
+  </si>
+  <si>
+    <t>exam</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -643,18 +668,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -674,6 +687,15 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="cover-test"/&gt;
+    &lt;display value="Cover test"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -1066,9 +1088,6 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -1078,7 +1097,7 @@
     <t>bodySiteEye</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
 </t>
   </si>
   <si>
@@ -1606,6 +1625,15 @@
     <t>With or without correction</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="correction-status"/&gt;
+    &lt;display value="Refractive correction status during test"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.component:correctionStatus.value[x]</t>
   </si>
   <si>
@@ -1636,10 +1664,22 @@
     <t>Observation.component:testDistance.code</t>
   </si>
   <si>
-    <t>Near or far</t>
+    <t>Near or far (categorical; near about 33-40 cm, far about 6 m / 20 ft)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="test-distance-category"/&gt;
+    &lt;display value="Testing distance category (near/far)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:testDistance.value[x]</t>
+  </si>
+  <si>
+    <t>https://YasniiSS.github.io/fhir4eyes/ValueSet/test-distance-category-vs</t>
   </si>
   <si>
     <t>Observation.component:testDistance.dataAbsentReason</t>
@@ -1973,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP78"/>
+  <dimension ref="A1:AP79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.8125" customWidth="true" bestFit="true"/>
@@ -2001,7 +2041,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.55078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -3709,7 +3749,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>191</v>
       </c>
@@ -3759,7 +3799,7 @@
         <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>83</v>
@@ -3777,25 +3817,23 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>191</v>
@@ -3822,10 +3860,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3833,14 +3871,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3856,22 +3896,22 @@
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3881,7 +3921,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3896,13 +3936,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3920,13 +3960,13 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -3935,34 +3975,34 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3981,19 +4021,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -4003,7 +4043,7 @@
         <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>83</v>
@@ -4018,13 +4058,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4042,10 +4082,10 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>94</v>
@@ -4057,30 +4097,30 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>83</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4088,13 +4128,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>83</v>
@@ -4103,18 +4143,20 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4162,13 +4204,13 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>83</v>
@@ -4177,19 +4219,19 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4197,21 +4239,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>234</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -4223,20 +4265,18 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4284,13 +4324,13 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
@@ -4299,19 +4339,19 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4319,14 +4359,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4345,19 +4385,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4406,7 +4446,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4421,19 +4461,19 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
@@ -4441,14 +4481,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4467,18 +4507,20 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4526,7 +4568,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4541,19 +4583,19 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4561,10 +4603,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4575,7 +4617,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4587,18 +4629,18 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4646,13 +4688,13 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
@@ -4661,30 +4703,30 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
+      <c r="A23" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4695,10 +4737,10 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>83</v>
@@ -4707,19 +4749,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4768,45 +4808,45 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4820,28 +4860,28 @@
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4866,13 +4906,13 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4890,7 +4930,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4899,7 +4939,7 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
@@ -4908,38 +4948,38 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4954,16 +4994,16 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4988,40 +5028,40 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
@@ -5030,31 +5070,31 @@
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5073,19 +5113,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5110,13 +5150,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5134,7 +5174,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5152,27 +5192,27 @@
         <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5183,10 +5223,10 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>83</v>
@@ -5195,18 +5235,20 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5230,13 +5272,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5254,13 +5296,13 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>83</v>
@@ -5272,27 +5314,27 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5306,7 +5348,7 @@
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
@@ -5315,15 +5357,17 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>324</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5348,13 +5392,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5372,7 +5416,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5384,44 +5428,44 @@
         <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5433,17 +5477,15 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5480,73 +5522,71 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AC29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AG29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AF29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>83</v>
@@ -5555,15 +5595,17 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>337</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>338</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5600,19 +5642,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5636,7 +5678,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5645,14 +5687,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="B31" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5664,7 +5708,7 @@
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>83</v>
@@ -5673,13 +5717,13 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5730,19 +5774,19 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
@@ -5754,7 +5798,7 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>328</v>
+        <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5765,10 +5809,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5779,7 +5823,7 @@
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5791,13 +5835,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5836,43 +5880,43 @@
         <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AC32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AD32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE32" t="s" s="2">
+      <c r="AG32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5894,10 +5938,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5909,7 +5953,7 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>348</v>
@@ -5917,16 +5961,14 @@
       <c r="M33" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -5956,31 +5998,31 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -5992,7 +6034,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6003,10 +6045,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6029,22 +6071,24 @@
         <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>355</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6086,10 +6130,10 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>94</v>
@@ -6098,7 +6142,7 @@
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6121,10 +6165,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6132,10 +6176,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6144,23 +6188,19 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6208,13 +6248,13 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -6229,10 +6269,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>367</v>
+        <v>137</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6243,10 +6283,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6257,7 +6297,7 @@
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6269,19 +6309,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6330,13 +6370,13 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
@@ -6351,10 +6391,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6365,10 +6405,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6388,22 +6428,22 @@
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>329</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6428,13 +6468,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6452,7 +6492,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6473,10 +6513,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6487,10 +6527,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6513,18 +6553,20 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>386</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6548,13 +6590,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6572,7 +6614,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6590,27 +6632,27 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6633,16 +6675,16 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6692,7 +6734,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6710,27 +6752,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6741,7 +6783,7 @@
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>83</v>
@@ -6753,20 +6795,18 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6814,45 +6854,45 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM40" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6863,7 +6903,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6875,16 +6915,20 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6932,19 +6976,19 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>407</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>83</v>
+        <v>413</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -6953,10 +6997,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>414</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>328</v>
+        <v>415</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6967,21 +7011,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6993,17 +7037,15 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7052,19 +7094,19 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -7076,7 +7118,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7087,14 +7129,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7107,26 +7149,24 @@
         <v>83</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7174,7 +7214,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7198,7 +7238,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7209,42 +7249,46 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7292,19 +7336,19 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>423</v>
+        <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7313,10 +7357,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>425</v>
+        <v>137</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7327,10 +7371,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7353,13 +7397,13 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7410,7 +7454,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7419,7 +7463,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7431,7 +7475,7 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>429</v>
@@ -7471,7 +7515,7 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>192</v>
+        <v>424</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>431</v>
@@ -7479,12 +7523,8 @@
       <c r="M46" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>434</v>
-      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7508,13 +7548,13 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>435</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>436</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -7541,7 +7581,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7550,13 +7590,13 @@
         <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>437</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>303</v>
+        <v>433</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7567,10 +7607,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7581,7 +7621,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7596,16 +7636,16 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7630,13 +7670,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7654,13 +7694,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -7672,13 +7712,13 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7689,10 +7729,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7703,7 +7743,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7715,17 +7755,19 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7750,13 +7792,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>448</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>449</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7774,13 +7816,13 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
@@ -7792,13 +7834,13 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>441</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>451</v>
+        <v>308</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7809,10 +7851,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7835,16 +7877,18 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>324</v>
+        <v>451</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7892,7 +7936,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7913,7 +7957,7 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>455</v>
@@ -7941,7 +7985,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7950,20 +7994,18 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8018,7 +8060,7 @@
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
@@ -8033,10 +8075,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>461</v>
+        <v>428</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8047,10 +8089,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8073,16 +8115,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8132,7 +8174,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8153,10 +8195,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8167,10 +8209,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8193,20 +8235,18 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>404</v>
+        <v>468</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>473</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8242,17 +8282,19 @@
         <v>83</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AC52" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8273,10 +8315,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8287,10 +8329,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8301,7 +8343,7 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8310,19 +8352,23 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8358,31 +8404,29 @@
         <v>83</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>83</v>
@@ -8391,10 +8435,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>328</v>
+        <v>480</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8405,21 +8449,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8431,17 +8475,15 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8490,19 +8532,19 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -8514,7 +8556,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8525,14 +8567,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8545,26 +8587,24 @@
         <v>83</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O55" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8612,7 +8652,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8636,7 +8676,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8647,45 +8687,45 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>481</v>
+        <v>420</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8710,13 +8750,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8734,34 +8774,34 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -8769,10 +8809,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8780,7 +8820,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>94</v>
@@ -8795,19 +8835,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8832,13 +8872,13 @@
         <v>83</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -8856,10 +8896,10 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>94</v>
@@ -8874,27 +8914,27 @@
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8914,22 +8954,22 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>490</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>491</v>
       </c>
       <c r="M58" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N58" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="O58" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8954,13 +8994,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -8978,7 +9018,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8987,7 +9027,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -8996,19 +9036,19 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -9020,14 +9060,14 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
@@ -9042,16 +9082,16 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>296</v>
+        <v>496</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>297</v>
+        <v>497</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9076,13 +9116,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9106,10 +9146,10 @@
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9118,31 +9158,31 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9161,19 +9201,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>496</v>
+        <v>300</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>497</v>
+        <v>301</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9198,13 +9238,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9222,7 +9262,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9240,31 +9280,29 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C61" t="s" s="2">
         <v>499</v>
       </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9273,31 +9311,31 @@
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9346,7 +9384,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9367,10 +9405,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>475</v>
+        <v>414</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9379,14 +9417,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9398,25 +9438,29 @@
         <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9464,19 +9508,19 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
@@ -9485,10 +9529,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>328</v>
+        <v>480</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9499,21 +9543,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>83</v>
@@ -9525,17 +9569,15 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9584,19 +9626,19 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>83</v>
@@ -9608,7 +9650,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9619,14 +9661,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9639,26 +9681,24 @@
         <v>83</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O64" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -9706,7 +9746,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9730,7 +9770,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9741,45 +9781,45 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>504</v>
+        <v>420</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -9804,13 +9844,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -9828,34 +9868,34 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9863,10 +9903,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9874,7 +9914,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>94</v>
@@ -9892,16 +9932,16 @@
         <v>192</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="O66" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -9911,7 +9951,7 @@
         <v>83</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>83</v>
@@ -9926,13 +9966,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -9950,10 +9990,10 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>94</v>
@@ -9968,27 +10008,27 @@
         <v>83</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10008,7 +10048,7 @@
         <v>83</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>192</v>
@@ -10017,13 +10057,13 @@
         <v>491</v>
       </c>
       <c r="M67" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N67" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="O67" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10048,13 +10088,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -10072,7 +10112,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10081,7 +10121,7 @@
         <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -10090,38 +10130,38 @@
         <v>83</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>494</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>83</v>
@@ -10136,16 +10176,16 @@
         <v>192</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>296</v>
+        <v>496</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>297</v>
+        <v>497</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10170,13 +10210,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10200,10 +10240,10 @@
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -10212,31 +10252,31 @@
         <v>83</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10255,19 +10295,19 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>496</v>
+        <v>300</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>497</v>
+        <v>301</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10292,13 +10332,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10316,7 +10356,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10334,31 +10374,29 @@
         <v>83</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>83</v>
       </c>
@@ -10367,31 +10405,31 @@
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>473</v>
+        <v>412</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10440,7 +10478,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10461,10 +10499,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>475</v>
+        <v>414</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10473,14 +10511,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10492,25 +10532,29 @@
         <v>94</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10558,19 +10602,19 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>83</v>
@@ -10579,10 +10623,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>328</v>
+        <v>480</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10593,21 +10637,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>83</v>
@@ -10619,17 +10663,15 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10678,19 +10720,19 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -10702,7 +10744,7 @@
         <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10713,14 +10755,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10733,26 +10775,24 @@
         <v>83</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O73" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>83</v>
       </c>
@@ -10800,7 +10840,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10824,7 +10864,7 @@
         <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10835,45 +10875,45 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>515</v>
+        <v>420</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10898,13 +10938,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10922,34 +10962,34 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -10957,10 +10997,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10968,7 +11008,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>94</v>
@@ -10986,16 +11026,16 @@
         <v>192</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11005,7 +11045,7 @@
         <v>83</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>83</v>
+        <v>521</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>83</v>
@@ -11020,13 +11060,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11044,10 +11084,10 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>94</v>
@@ -11062,27 +11102,27 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11102,7 +11142,7 @@
         <v>83</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>192</v>
@@ -11111,13 +11151,13 @@
         <v>491</v>
       </c>
       <c r="M76" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N76" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="O76" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11142,13 +11182,11 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>290</v>
+        <v>523</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11166,7 +11204,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11175,7 +11213,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -11184,38 +11222,38 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>494</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11230,16 +11268,16 @@
         <v>192</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>296</v>
+        <v>496</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>297</v>
+        <v>497</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11264,13 +11302,13 @@
         <v>83</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -11294,10 +11332,10 @@
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -11306,31 +11344,31 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11349,19 +11387,19 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>496</v>
+        <v>300</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>497</v>
+        <v>301</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11386,13 +11424,13 @@
         <v>83</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>83</v>
@@ -11410,7 +11448,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11428,23 +11466,145 @@
         <v>83</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN78" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AO78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP78" t="s" s="2">
+      <c r="O79" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP78">
+  <autoFilter ref="A1:AP79">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11454,7 +11614,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
